--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4934-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4934-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EAD5F1B-6D32-4193-B235-826E2B2C6763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE2280CC-DD95-418D-817F-64FD1186859C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{EC344FD8-191E-49C4-B4CA-E8F6D358EFB1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{28322537-E740-4E18-B3AA-1DCBFF160F64}"/>
   </bookViews>
   <sheets>
     <sheet name="4934-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1433,24 +1433,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CCA34C-126A-46F0-B0F7-C0568F0089B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD4948F-DA52-419B-96BF-FEAC8E40C46C}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1604,7 +1604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2019</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2018</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2017</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2016</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2015</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2014</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2013</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2012</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2011</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2010</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
         <v>30</v>
       </c>
